--- a/MechanismOfAction/BCIO-moa-hierarchy.xlsx
+++ b/MechanismOfAction/BCIO-moa-hierarchy.xlsx
@@ -587,7 +587,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+          <t>A &lt;role&gt; that inheres in a human being by virtue of their social and institutional circumstances.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -1711,7 +1711,7 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>A &lt;disposition&gt; which is realised by an environmental system or system parts thereof.</t>
+          <t>A disposition which is realised by an environmental system or system parts thereof.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2949,7 +2949,7 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>A &lt;personal capability&gt; that  includes mental processes in its realisation.</t>
+          <t>A personal capability that includes mental processes in its realisation.</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -4203,7 +4203,7 @@
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>A bodily disposition which is realised as impaired functioning following reduction or termination of use of a psychoactive substance as a result of long-term physiological adaptation to that substance.</t>
+          <t>A &lt;bodily disposition&gt; which is realised as impaired functioning following reduction or termination of use of a psychoactive substance.</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>A &lt;bodily disposition&gt; that is realized in a mental process.</t>
+          <t xml:space="preserve">A mental disposition is a bodily disposition that is realized in a mental process. </t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -5928,7 +5928,7 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>A &lt;mental disposition&gt; to represent a proposition to be true.</t>
+          <t>A mental disposition to represent a proposition to be true.</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -14098,7 +14098,7 @@
       <c r="N333" t="inlineStr"/>
       <c r="O333" t="inlineStr">
         <is>
-          <t>An appraisal that represents an evaluation that an event was caused by oneself.</t>
+          <t>An &lt;appraisal of causal agency&gt; that represents an evaluation that an event was caused by oneself.</t>
         </is>
       </c>
       <c r="R333" t="inlineStr"/>
@@ -14167,7 +14167,7 @@
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr">
         <is>
-          <t>An affective appraisal which represents an evaluation of how threatening an object or situation is.</t>
+          <t>An &lt;emotional-relevance appraisal&gt; which represents an evaluation of how threatening an object or situation is.</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
@@ -14385,7 +14385,7 @@
       <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr">
         <is>
-          <t>An appraisal of desirability that represents an evaluation of the desirability of the expected consequences of an event.</t>
+          <t>An &lt;appraisal of desirability&gt; that represents an evaluation of the desirability of the expected consequences of an event.</t>
         </is>
       </c>
       <c r="R341" t="inlineStr"/>
@@ -14463,7 +14463,7 @@
       <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+          <t>A &lt;cognitive representation&gt; of themselves by a person or group.</t>
         </is>
       </c>
       <c r="R343" t="inlineStr"/>
@@ -14546,7 +14546,7 @@
       <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr">
         <is>
-          <t>An identity that a person has about themselves.</t>
+          <t>An &lt;identity&gt; that a person has about themselves.</t>
         </is>
       </c>
       <c r="R345" t="inlineStr"/>
@@ -14587,7 +14587,7 @@
       <c r="N346" t="inlineStr"/>
       <c r="O346" t="inlineStr">
         <is>
-          <t>A self-identity that represents a relation between oneself and another person or group.</t>
+          <t>A &lt;self-identity&gt; that represents a relation between oneself and another person or group</t>
         </is>
       </c>
       <c r="P346" t="inlineStr">
@@ -14936,7 +14936,7 @@
       <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
@@ -15245,7 +15245,7 @@
       <c r="N363" t="inlineStr"/>
       <c r="O363" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
       <c r="R363" t="inlineStr"/>
@@ -15371,7 +15371,7 @@
       <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr">
         <is>
-          <t>A material entity consisting of multiple components that are causally integrated.</t>
+          <t>A &lt;material entity&gt; consisting of multiple components that are causally integrated.</t>
         </is>
       </c>
       <c r="R366" t="inlineStr"/>
@@ -15449,7 +15449,7 @@
       <c r="N368" t="inlineStr"/>
       <c r="O368" t="inlineStr">
         <is>
-          <t>A &lt;system&gt; which has the disposition to surround and interact with one or more material entities.</t>
+          <t>A system which has the disposition to environ one or more material entities.</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
@@ -15975,7 +15975,7 @@
       <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr">
         <is>
-          <t>An environmental system which includes both living and non-living components.</t>
+          <t>An &lt;environmental system&gt; which includes both living and non-living components.</t>
         </is>
       </c>
       <c r="R380" t="inlineStr"/>
@@ -16848,7 +16848,7 @@
       <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -16895,7 +16895,7 @@
       <c r="N406" t="inlineStr"/>
       <c r="O406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valence is a process profile of an emotion, mood, or affective bodily feeling (such as pleasure and pain). Valence can be positive or negative, with different strengths in both directions. For example, pleasure is positively valenced while pain is negatively valenced.  </t>
+          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
         </is>
       </c>
       <c r="Q406" t="inlineStr">
@@ -17198,7 +17198,7 @@
       <c r="N413" t="inlineStr"/>
       <c r="O413" t="inlineStr">
         <is>
-          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+          <t>A mental process that has positive or negative valence.</t>
         </is>
       </c>
       <c r="P413" t="inlineStr">
@@ -17244,7 +17244,7 @@
       <c r="N414" t="inlineStr"/>
       <c r="O414" t="inlineStr">
         <is>
-          <t>The subjective emotional feeling is that (fiat) part of the emotion process by which the organism experiences its own emotion.</t>
+          <t>An &lt;affective process&gt; that involves the experience of internal or external sensory stimuli.</t>
         </is>
       </c>
       <c r="P414" t="inlineStr">
@@ -17422,7 +17422,7 @@
       <c r="N418" t="inlineStr"/>
       <c r="O418" t="inlineStr">
         <is>
-          <t>A &lt;subjective affective feeling&gt; of tiredness, needing sleep.</t>
+          <t>A subjective affective feeling of a need for sleep.</t>
         </is>
       </c>
       <c r="R418" t="inlineStr"/>
@@ -17459,7 +17459,7 @@
       <c r="N419" t="inlineStr"/>
       <c r="O419" t="inlineStr">
         <is>
-          <t>&lt;Feeling tired&gt; to an extremely strong degree.</t>
+          <t>Feeling tired to an extremely strong degree.</t>
         </is>
       </c>
       <c r="R419" t="inlineStr"/>
@@ -17496,7 +17496,7 @@
       <c r="N420" t="inlineStr"/>
       <c r="O420" t="inlineStr">
         <is>
-          <t>A subjective affective feeling of having lots of energy, being energetic.</t>
+          <t>A &lt;subjective affective feeling&gt; of having lots of energy, being energetic.</t>
         </is>
       </c>
       <c r="R420" t="inlineStr"/>
@@ -17574,7 +17574,7 @@
       <c r="N422" t="inlineStr"/>
       <c r="O422" t="inlineStr">
         <is>
-          <t>A &lt;subjective affective feeling&gt; of being at ease, comfortable, relaxed.</t>
+          <t>A subjective affective feeling of being at ease, comfortable, relaxed.</t>
         </is>
       </c>
       <c r="R422" t="inlineStr"/>
@@ -17722,9 +17722,7 @@
       <c r="N426" t="inlineStr"/>
       <c r="O426" t="inlineStr">
         <is>
-          <t>A subjective affective feeling in an organism S, involving two integrated levels: 
-(a) activation of the nociceptive system and associated emotion generating brain components of S, and 
-(b) a simultaneous aversive sensory and emotional experience on the part of S, where (b) is phenomenologically similar to the sort of aversive experience involved in pain with concordant tissue damage.</t>
+          <t>A &lt;subjective affective feeling&gt; in an organism S, involving two integrated levels: (a) activation of the nociceptive system and associated emotion generating brain components of S, and (b) a simultaneous aversive sensory and emotional experience on the part of S, where (b) is phenomenologically similar to the sort of aversive experience involved in pain with concordant tissue damage.</t>
         </is>
       </c>
       <c r="Q426" t="inlineStr">
@@ -17766,7 +17764,7 @@
       <c r="N427" t="inlineStr"/>
       <c r="O427" t="inlineStr">
         <is>
-          <t>A &lt;subjective affective feeling&gt; that involves discomfort and is associated with a need to consume food.</t>
+          <t>A subjective affective feeling that involves discomfort and is associated with a need to consume food.</t>
         </is>
       </c>
       <c r="R427" t="inlineStr"/>
@@ -18356,7 +18354,7 @@
       <c r="N442" t="inlineStr"/>
       <c r="O442" t="inlineStr">
         <is>
-          <t>&lt;Surprise&gt; with a positive valence.</t>
+          <t>Surprise with a positive valence</t>
         </is>
       </c>
       <c r="R442" t="inlineStr">
@@ -18668,7 +18666,7 @@
       <c r="N450" t="inlineStr"/>
       <c r="O450" t="inlineStr">
         <is>
-          <t>&lt;Disgust&gt; elicited by "contaminated" food substances: rotten food, culturally variable "bad" food, certain animals associated with rotten food (maggots, rats), and every body product except tears.</t>
+          <t>Disgust elicited by "contaminated" food substances: rotten food, culturally variable "bad" food, certain animals associated with rotten food (maggots, rats), and every body product except tears. [Source: OCEAS]</t>
         </is>
       </c>
       <c r="R450" t="inlineStr"/>
@@ -18742,7 +18740,7 @@
       <c r="N452" t="inlineStr"/>
       <c r="O452" t="inlineStr">
         <is>
-          <t>Disgust elicited by poor hygiene, inappropriate sex, gore or violations of bodily boundaries, and death or the odor of decay. [Source: OCEAS]</t>
+          <t>&lt;Disgust&gt; elicited by poor hygiene, inappropriate sex, gore or violations of bodily boundaries, and death or the odor of decay.</t>
         </is>
       </c>
       <c r="R452" t="inlineStr"/>
@@ -19218,7 +19216,7 @@
       <c r="N464" t="inlineStr"/>
       <c r="O464" t="inlineStr">
         <is>
-          <t>A &lt;mental process&gt; that involves heightened responding to an internal or external stimulus.</t>
+          <t>A mental process that is the psychological and physiological state of being awake and reactive to stimuli.</t>
         </is>
       </c>
       <c r="R464" t="inlineStr"/>
@@ -19432,7 +19430,7 @@
       <c r="N469" t="inlineStr"/>
       <c r="O469" t="inlineStr">
         <is>
-          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
+          <t>A &lt;mental process&gt; that creates, modifies or has as participant some cognitive representation.</t>
         </is>
       </c>
       <c r="R469" t="inlineStr"/>
@@ -19469,7 +19467,7 @@
       <c r="N470" t="inlineStr"/>
       <c r="O470" t="inlineStr">
         <is>
-          <t>a mental process that involves the manipulation of mental language and/or mental images</t>
+          <t>A &lt;cognitive process&gt; that involves the manipulation of mental language and/or mental images.</t>
         </is>
       </c>
       <c r="R470" t="inlineStr"/>
@@ -20300,7 +20298,7 @@
       <c r="N491" t="inlineStr"/>
       <c r="O491" t="inlineStr">
         <is>
-          <t>A mental process that evokes the representation of the sensory characteristics of objects or events when these are not immediately present to the senses.</t>
+          <t>A &lt;mental process&gt; that evokes the representation of the sensory characteristics of objects or events when these are not immediately present to the senses.</t>
         </is>
       </c>
       <c r="R491" t="inlineStr"/>
@@ -20424,7 +20422,7 @@
       <c r="N494" t="inlineStr"/>
       <c r="O494" t="inlineStr">
         <is>
-          <t>An increase in a behavioural response to a repeated stimulus.</t>
+          <t>An increased in a behavioral response to a repeated stimulus. For example, a shock to the tail of the marine snail Aplysia, to which the snail responds by withdrawing its gill, will result in increased gill withdrawal the next time the skin is touched.</t>
         </is>
       </c>
       <c r="R494" t="inlineStr"/>
@@ -22519,7 +22517,7 @@
       <c r="N545" t="inlineStr"/>
       <c r="O545" t="inlineStr">
         <is>
-          <t>A &lt;mental process&gt; that involves thinking about a state of affairs that is not yet the case together with a desire for that state of affairs to come about.</t>
+          <t>A mental process that involves thinking about a state of affairs that is not yet the case together with a desire for that state of affairs to come about.</t>
         </is>
       </c>
       <c r="R545" t="inlineStr"/>
@@ -22776,7 +22774,7 @@
       <c r="N551" t="inlineStr"/>
       <c r="O551" t="inlineStr">
         <is>
-          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
+          <t>A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.</t>
         </is>
       </c>
       <c r="R551" t="inlineStr"/>
@@ -23408,7 +23406,7 @@
       <c r="N567" t="inlineStr"/>
       <c r="O567" t="inlineStr">
         <is>
-          <t>A mental process that gives rise to an appraisal.</t>
+          <t>A &lt;mental process&gt; that gives rise to an appraisal.</t>
         </is>
       </c>
       <c r="Q567" t="inlineStr">
@@ -24301,7 +24299,7 @@
       <c r="N590" t="inlineStr"/>
       <c r="O590" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+          <t>A &lt;bodily process&gt; of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
         </is>
       </c>
       <c r="Q590" t="inlineStr">
@@ -24343,7 +24341,7 @@
       <c r="N591" t="inlineStr"/>
       <c r="O591" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
+          <t>An &lt;individual human behaviour&gt; that relates to the social environment.</t>
         </is>
       </c>
       <c r="R591" t="inlineStr"/>
@@ -24421,7 +24419,7 @@
       <c r="N593" t="inlineStr"/>
       <c r="O593" t="inlineStr">
         <is>
-          <t>An &lt;expressive behaviour&gt; that involves the transmission of information between two or more people.</t>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
         </is>
       </c>
       <c r="R593" t="inlineStr"/>
@@ -24462,7 +24460,7 @@
       <c r="N594" t="inlineStr"/>
       <c r="O594" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+          <t>A &lt;human communication behaviour&gt; in which the information that is communicated is encoded in language.</t>
         </is>
       </c>
       <c r="R594" t="inlineStr"/>
@@ -24503,7 +24501,7 @@
       <c r="N595" t="inlineStr"/>
       <c r="O595" t="inlineStr">
         <is>
-          <t>A &lt;human communication behaviour&gt; in which information is transmitted without being encoded in the meaning units of any language.</t>
+          <t>A human communication behaviour in which information is transmitted without being encoded in the meaning units of any language.</t>
         </is>
       </c>
       <c r="R595" t="inlineStr"/>
@@ -24884,7 +24882,7 @@
       <c r="N604" t="inlineStr"/>
       <c r="O604" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
+          <t>An &lt;individual human behaviour&gt; that conveys a thought or feeling.</t>
         </is>
       </c>
       <c r="R604" t="inlineStr"/>
@@ -25175,7 +25173,7 @@
       <c r="N612" t="inlineStr"/>
       <c r="O612" t="inlineStr">
         <is>
-          <t>A &lt;bodily process&gt; in which at least two human beings are agents.</t>
+          <t>A process in which at least two human beings are agents.</t>
         </is>
       </c>
       <c r="R612" t="inlineStr">
